--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="155">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -357,6 +357,21 @@
   </si>
   <si>
     <t xml:space="preserve">VTX-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">az</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azrasizzle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アズラシズル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inpure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不浄なるもの</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -585,7 +600,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -606,10 +621,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -620,7 +635,7 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -634,14 +649,14 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -655,10 +670,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -669,7 +684,7 @@
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -683,10 +698,10 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -704,10 +719,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -725,10 +740,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -746,10 +761,10 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
@@ -767,10 +782,10 @@
         <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -788,10 +803,10 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
@@ -809,10 +824,10 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -830,10 +845,10 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -851,10 +866,10 @@
         <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
         <v>47</v>
@@ -872,10 +887,10 @@
         <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -893,10 +908,10 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
         <v>52</v>
@@ -914,10 +929,10 @@
         <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
         <v>41</v>
@@ -935,10 +950,10 @@
         <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -956,10 +971,10 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
         <v>59</v>
@@ -977,10 +992,10 @@
         <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
         <v>62</v>
@@ -998,10 +1013,10 @@
         <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
@@ -1019,10 +1034,10 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
         <v>68</v>
@@ -1033,7 +1048,7 @@
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J23" t="s">
         <v>70</v>
@@ -1047,10 +1062,10 @@
         <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>73</v>
@@ -1068,7 +1083,7 @@
         <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -1082,10 +1097,10 @@
         <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
         <v>77</v>
@@ -1103,10 +1118,10 @@
         <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -1124,10 +1139,10 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D28" t="s">
         <v>83</v>
@@ -1145,10 +1160,10 @@
         <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
         <v>86</v>
@@ -1166,10 +1181,10 @@
         <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
         <v>86</v>
@@ -1187,10 +1202,10 @@
         <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D31" t="s">
         <v>90</v>
@@ -1208,10 +1223,10 @@
         <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -1229,10 +1244,10 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
         <v>96</v>
@@ -1250,10 +1265,10 @@
         <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
         <v>99</v>
@@ -1271,10 +1286,10 @@
         <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
         <v>102</v>
@@ -1292,10 +1307,10 @@
         <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
         <v>102</v>
@@ -1313,10 +1328,10 @@
         <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
         <v>106</v>
@@ -1334,10 +1349,10 @@
         <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
         <v>109</v>
@@ -1355,7 +1370,7 @@
         <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
         <v>112</v>
@@ -1376,6 +1391,28 @@
       </c>
       <c r="K39" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="J40" t="s">
+        <v>117</v>
+      </c>
+      <c r="K40" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>

--- a/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="163">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -372,6 +372,21 @@
   </si>
   <si>
     <t xml:space="preserve">不浄なるもの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pebble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pebble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石ころ</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -609,7 +624,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -630,10 +645,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -644,7 +659,7 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -658,14 +673,14 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -679,10 +694,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -693,7 +708,7 @@
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -707,10 +722,10 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -728,10 +743,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -749,10 +764,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -770,10 +785,10 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
@@ -791,10 +806,10 @@
         <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -812,10 +827,10 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
@@ -833,10 +848,10 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -854,10 +869,10 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -875,10 +890,10 @@
         <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
         <v>47</v>
@@ -896,10 +911,10 @@
         <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -917,10 +932,10 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
         <v>52</v>
@@ -938,10 +953,10 @@
         <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
         <v>41</v>
@@ -959,10 +974,10 @@
         <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -980,10 +995,10 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
         <v>59</v>
@@ -1001,10 +1016,10 @@
         <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
         <v>62</v>
@@ -1022,10 +1037,10 @@
         <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
@@ -1043,10 +1058,10 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
         <v>68</v>
@@ -1057,7 +1072,7 @@
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J23" t="s">
         <v>70</v>
@@ -1071,10 +1086,10 @@
         <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D24" t="s">
         <v>73</v>
@@ -1092,7 +1107,7 @@
         <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -1106,10 +1121,10 @@
         <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
         <v>77</v>
@@ -1127,10 +1142,10 @@
         <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -1148,10 +1163,10 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
         <v>83</v>
@@ -1169,10 +1184,10 @@
         <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>86</v>
@@ -1190,10 +1205,10 @@
         <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
         <v>86</v>
@@ -1211,10 +1226,10 @@
         <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
         <v>90</v>
@@ -1232,10 +1247,10 @@
         <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -1253,10 +1268,10 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s">
         <v>96</v>
@@ -1274,10 +1289,10 @@
         <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
         <v>99</v>
@@ -1295,10 +1310,10 @@
         <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
         <v>102</v>
@@ -1316,10 +1331,10 @@
         <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D36" t="s">
         <v>102</v>
@@ -1337,10 +1352,10 @@
         <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
         <v>106</v>
@@ -1358,10 +1373,10 @@
         <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
         <v>109</v>
@@ -1379,7 +1394,7 @@
         <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
         <v>112</v>
@@ -1407,10 +1422,10 @@
         <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
         <v>115</v>
@@ -1421,7 +1436,7 @@
       <c r="G40"/>
       <c r="H40"/>
       <c r="I40" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J40" t="s">
         <v>117</v>
@@ -1429,6 +1444,42 @@
       <c r="K40" t="s">
         <v>118</v>
       </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" t="s">
+        <v>123</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="J42"/>
+      <c r="K42"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K2"/>
